--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david4F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线4层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>stop</t>
   </si>
   <si>
     <t>bgfade(sntzm_david4F(3)_1,1)</t>
@@ -249,6 +252,9 @@
     <t>没等你来得及发出一句疑问，两张屏幕上便各自闪出一只人影，它们就像后台准备就绪的演员，在观众目光就位的那一刻准时出现在属于自己的位置——</t>
   </si>
   <si>
+    <t>18 enhanced_APPLE</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=9</t>
   </si>
   <si>
@@ -393,6 +399,9 @@
     <t>看到房间中央的两个按钮了吗？</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Abaddon; 层级=23</t>
   </si>
   <si>
@@ -646,6 +655,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(R,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -748,6 +762,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2886,30 +2905,30 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="150" spans="1:12">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -2918,7 +2937,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2930,24 +2949,24 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -2956,7 +2975,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2968,15 +2987,15 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="42" spans="1:12">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2994,7 +3013,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3009,12 +3028,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3032,7 +3051,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3047,12 +3066,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3070,13 +3089,13 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -3085,12 +3104,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3108,7 +3127,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3120,18 +3139,18 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -3146,7 +3165,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3161,12 +3180,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="55.5" spans="1:12">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3184,13 +3203,13 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
@@ -3199,12 +3218,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="54" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3222,7 +3241,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3234,21 +3253,21 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="30" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3257,7 +3276,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3269,15 +3288,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3286,7 +3305,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3295,7 +3314,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3307,15 +3326,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:12">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3333,7 +3352,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3348,12 +3367,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3371,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3386,12 +3405,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="54" spans="1:12">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3409,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3421,24 +3440,24 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:12">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3447,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3459,15 +3478,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="43.5" spans="1:12">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3476,7 +3495,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3485,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3497,15 +3516,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="55.5" spans="1:12">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3523,7 +3542,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3535,18 +3554,18 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="27" spans="1:12">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3561,7 +3580,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3576,12 +3595,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="55.5" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3599,7 +3618,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3614,21 +3633,21 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:12">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3637,7 +3656,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3649,15 +3668,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:12">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3666,45 +3685,45 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" ht="45" spans="1:12">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>94</v>
-      </c>
-      <c r="L24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:12">
-      <c r="A25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
       <c r="C25" t="s">
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3713,13 +3732,13 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -3728,21 +3747,21 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3751,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3766,12 +3785,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3780,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3789,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3804,21 +3823,21 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" ht="55.5" spans="1:12">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3827,7 +3846,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3839,30 +3858,30 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:12">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3874,15 +3893,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3897,10 +3916,10 @@
         <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3912,15 +3931,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L30" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3953,21 +3972,21 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="150" spans="1:12">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -3976,7 +3995,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3988,15 +4007,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" ht="30" spans="1:12">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4005,7 +4024,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -4014,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4026,15 +4045,15 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" ht="55.5" spans="1:12">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4052,7 +4071,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4067,12 +4086,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:12">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4090,7 +4109,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4105,21 +4124,21 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" ht="42" spans="1:12">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4128,7 +4147,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4140,15 +4159,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4157,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4166,7 +4185,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4178,24 +4197,24 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L37" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" ht="30" spans="1:12">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4204,7 +4223,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4216,24 +4235,24 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" ht="30" spans="1:12">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4242,7 +4261,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4257,21 +4276,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" ht="30" spans="1:12">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4280,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4295,12 +4314,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4309,7 +4328,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4318,7 +4337,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4330,24 +4349,24 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L41" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" ht="42" spans="1:12">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4356,7 +4375,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4368,15 +4387,15 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L42" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" ht="40.5" spans="1:12">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4385,7 +4404,7 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4394,7 +4413,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4406,24 +4425,24 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L43" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4432,7 +4451,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4444,24 +4463,24 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" ht="30" spans="1:12">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4470,7 +4489,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4482,12 +4501,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4496,7 +4515,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4505,7 +4524,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4520,21 +4539,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" ht="70.5" spans="1:12">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4543,7 +4562,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4558,21 +4577,21 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" ht="30" spans="1:12">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4581,7 +4600,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4593,15 +4612,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L48" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" ht="54" spans="1:12">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4619,7 +4638,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4634,21 +4653,21 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4657,7 +4676,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4669,33 +4688,33 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L50" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" ht="30" spans="1:12">
       <c r="A51" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4707,15 +4726,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L51" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4730,10 +4749,10 @@
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4745,24 +4764,24 @@
         <v>15</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L52" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4771,7 +4790,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4783,24 +4802,24 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L53" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4809,7 +4828,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4821,24 +4840,24 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L54" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4847,7 +4866,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4859,15 +4878,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4876,7 +4895,7 @@
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4885,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4900,21 +4919,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4923,7 +4942,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4938,21 +4957,21 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4961,7 +4980,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4976,21 +4995,21 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" ht="30" spans="1:12">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -4999,7 +5018,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5014,21 +5033,21 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" ht="67.5" spans="1:12">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5037,7 +5056,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5052,21 +5071,21 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" ht="55.5" spans="1:12">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5075,7 +5094,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5090,12 +5109,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5104,7 +5123,7 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5113,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5125,15 +5144,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L62" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" ht="54" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5151,7 +5170,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5163,24 +5182,24 @@
         <v>15</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L63" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" ht="150" spans="1:12">
       <c r="A64" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5189,7 +5208,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5201,15 +5220,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L64" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5218,7 +5237,7 @@
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5227,7 +5246,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5242,21 +5261,21 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5265,7 +5284,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5280,12 +5299,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5294,7 +5313,7 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5303,7 +5322,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5318,21 +5337,21 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5341,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5356,12 +5375,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5370,7 +5389,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5379,7 +5398,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5391,18 +5410,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70" ht="27" spans="1:12">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5417,7 +5436,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5432,21 +5451,21 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5455,7 +5474,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5467,24 +5486,24 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5493,7 +5512,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5508,21 +5527,21 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" ht="30" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -5531,7 +5550,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5543,15 +5562,15 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L73" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" ht="57" spans="1:12">
       <c r="A74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5569,7 +5588,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5584,15 +5603,15 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -5607,7 +5626,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5622,21 +5641,21 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5645,7 +5664,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5657,15 +5676,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5674,7 +5693,7 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5683,7 +5702,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5698,21 +5717,21 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" ht="30" spans="1:12">
       <c r="A78" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -5721,7 +5740,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5736,12 +5755,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" ht="55.5" spans="1:12">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5750,7 +5769,7 @@
         <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -5759,7 +5778,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5771,15 +5790,15 @@
         <v>15</v>
       </c>
       <c r="K79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L79" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5797,7 +5816,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5812,21 +5831,21 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -5835,7 +5854,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5847,24 +5866,24 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L81" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" ht="40.5" spans="1:12">
       <c r="A82" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -5873,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5888,12 +5907,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83" ht="40.5" spans="1:12">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5902,7 +5921,7 @@
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -5911,7 +5930,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5923,24 +5942,24 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L83" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -5949,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5961,15 +5980,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L84" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="85" ht="30" spans="1:12">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5978,7 +5997,7 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E85" t="s">
         <v>15</v>
@@ -5987,7 +6006,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5999,15 +6018,15 @@
         <v>15</v>
       </c>
       <c r="K85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L85" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6025,7 +6044,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6040,21 +6059,21 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" ht="42" spans="1:12">
       <c r="A87" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -6063,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6075,33 +6094,33 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L87" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G88" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6113,15 +6132,15 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L88" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89" ht="55.5" spans="1:12">
       <c r="A89" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6136,10 +6155,10 @@
         <v>15</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G89" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6151,24 +6170,24 @@
         <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L89" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="90" ht="30" spans="1:12">
       <c r="A90" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6177,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6189,15 +6208,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L90" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6206,7 +6225,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6215,7 +6234,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6230,21 +6249,21 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E92" t="s">
         <v>15</v>
@@ -6253,7 +6272,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6268,30 +6287,30 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="93" ht="43.5" spans="1:12">
       <c r="A93" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G93" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6303,15 +6322,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L93" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="94" ht="43.5" spans="1:12">
       <c r="A94" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6326,10 +6345,10 @@
         <v>15</v>
       </c>
       <c r="F94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G94" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6341,24 +6360,24 @@
         <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -6367,7 +6386,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6379,10 +6398,10 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L95" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -6403,47 +6422,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -6451,74 +6470,74 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6540,616 +6559,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F6" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F7" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C10" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D10" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F10" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B12" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C12" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C13" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F13" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F14" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B16" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F16" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D18" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E18" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F18" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C19" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D19" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C20" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E20" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B21" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C21" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D21" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C22" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D22" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E22" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B23" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F23" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D24" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F24" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C25" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D25" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E25" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F25" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D26" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E26" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F26" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B27" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D27" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E27" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F27" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B28" t="s">
+        <v>463</v>
+      </c>
+      <c r="C28" t="s">
+        <v>464</v>
+      </c>
+      <c r="D28" t="s">
         <v>460</v>
       </c>
-      <c r="C28" t="s">
-        <v>461</v>
-      </c>
-      <c r="D28" t="s">
-        <v>457</v>
-      </c>
       <c r="E28" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F28" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B29" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C29" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D29" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E29" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F29" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C30" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D30" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E30" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F30" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B31" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D31" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
